--- a/reports/pdf_change_20260709.xlsx
+++ b/reports/pdf_change_20260709.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,034억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 3종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,389억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 3종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1840129200</v>
+        <v>1871200800</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-54</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-811076760</v>
+        <v>-824772240</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1670955000</v>
+        <v>1699170000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-25</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3616405000</v>
+        <v>-3677470000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1742910000</v>
+        <v>1772340000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-22</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-439255960</v>
+        <v>-446673040</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>-20</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-929552000</v>
+        <v>-945248000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>-16</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-448572800</v>
+        <v>-456147200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -856,23 +856,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-436846800</v>
+        <v>-1335921600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.42%</t>
+          <t>0.72%→0.42%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -884,23 +884,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1313738400</v>
+        <v>-444223200</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.42%</t>
+          <t>1.52%→1.42%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
         <v>-10</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-420537000</v>
+        <v>-427638000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1291139200</v>
+        <v>-1312940800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-417658800</v>
+        <v>-946332000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>1.30%→1.26%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -996,30 +996,30 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-930618000</v>
+        <v>-424711200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,657억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,354억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1043,7 +1043,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,176억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 3종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 3종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1139,7 +1139,7 @@
         <v>139</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>8249483200</v>
+        <v>8438884600</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>-81</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-4788201600</v>
+        <v>-4898134800</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1604691200</v>
+        <v>1641533600</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>-50</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-4025840000</v>
+        <v>-4118270000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1281840000</v>
+        <v>1311270000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1241,23 +1241,23 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-627200000</v>
+        <v>-2333820000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>9.07%→8.29%</t>
+          <t>2.85%→2.41%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>770→750</t>
+          <t>80→60</t>
         </is>
       </c>
     </row>
@@ -1269,23 +1269,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-2281440000</v>
+        <v>-641600000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.41%</t>
+          <t>9.07%→8.29%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>80→60</t>
+          <t>770→750</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
         <v>-10</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1063888000</v>
+        <v>-1088314000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>-9</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-240962400</v>
+        <v>-246494700</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,760억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,581억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1372,7 +1372,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 4종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 324억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1468,11 +1468,11 @@
         <v>121</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>90764520</v>
+        <v>84361200</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>6.61%→6.88%</t>
+          <t>6.60%→6.87%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1489,11 +1489,11 @@
         <v>-39</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-115642800</v>
+        <v>-110728800</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>6.13%→5.79%</t>
+          <t>6.30%→5.95%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1512,11 +1512,11 @@
         <v>12</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>113601600</v>
+        <v>103521600</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>2.35%→2.68%</t>
+          <t>2.30%→2.62%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1533,7 +1533,7 @@
         <v>-36</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-33596640</v>
+        <v>-31540320</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1556,11 +1556,11 @@
         <v>10</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>34860000</v>
+        <v>32130000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>1.16%→1.26%</t>
+          <t>1.15%→1.25%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1577,11 +1577,11 @@
         <v>-34</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-31073280</v>
+        <v>-29816640</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.13%</t>
+          <t>0.23%→0.13%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1600,11 +1600,11 @@
         <v>8</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>31147200</v>
+        <v>26880000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.23%→2.32%</t>
+          <t>2.06%→2.15%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1621,11 +1621,11 @@
         <v>-16</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-51744000</v>
+        <v>-48384000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.65%</t>
+          <t>0.81%→0.65%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>-14</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-36456000</v>
+        <v>-35103600</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 571억      당일 2026-07-09  vs  전영업일 2026-07-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>

--- a/reports/pdf_change_20260709.xlsx
+++ b/reports/pdf_change_20260709.xlsx
@@ -968,23 +968,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-946332000</v>
+        <v>-424711200</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -996,23 +996,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-424711200</v>
+        <v>-946332000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>1.30%→1.26%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260709.xlsx
+++ b/reports/pdf_change_20260709.xlsx
@@ -707,23 +707,23 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1699170000</v>
+        <v>1772340000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>3.89%→4.31%</t>
+          <t>2.95%→3.47%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1772340000</v>
+        <v>1699170000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.47%</t>
+          <t>3.89%→4.31%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1335921600</v>
+        <v>-444223200</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.42%</t>
+          <t>1.52%→1.42%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -884,23 +884,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-444223200</v>
+        <v>-1335921600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.42%</t>
+          <t>0.72%→0.42%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -968,23 +968,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-424711200</v>
+        <v>-946332000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>1.30%→1.26%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -996,23 +996,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-946332000</v>
+        <v>-424711200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.26%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260709.xlsx
+++ b/reports/pdf_change_20260709.xlsx
@@ -707,23 +707,23 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1772340000</v>
+        <v>1699170000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.47%</t>
+          <t>3.89%→4.31%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1699170000</v>
+        <v>1772340000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>3.89%→4.31%</t>
+          <t>2.95%→3.47%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -856,23 +856,23 @@
       <c r="E11" s="17" t="n"/>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-444223200</v>
+        <v>-1335921600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.42%</t>
+          <t>0.72%→0.42%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -884,23 +884,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1335921600</v>
+        <v>-444223200</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.42%</t>
+          <t>1.52%→1.42%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
